--- a/foundational_documents/DOT_signal_dictionary.xlsx
+++ b/foundational_documents/DOT_signal_dictionary.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -146,6 +151,8 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -511,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2582,6 +2589,103 @@
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>Volume_Ratio_10:lo + Micro_RollProxy:lo + Volume:hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE GAP ENTRIES (S.20) — lone-variable conviction; size book longs + fill gaps</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="15" t="n"/>
+      <c r="G63" s="15" t="n"/>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="15" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Trend-persistence extreme: the D2D long is a genuinely running trend — sizes book longs to 2x AND fires solo when the book is flat</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Micro_Hurst:hi@p97 · D2D+ (LOCK=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Failed break-down reverts upward: confirms the longs that follow AND fires a reversion-long in the gaps the book misses</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Micro_FailedBreak:hi@p90 · D2D- (LOCK=3)</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4460,6 +4564,78 @@
       </c>
       <c r="H51" s="9" t="n">
         <v>7.63</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>SV_FailBrk_L</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Failed break-down reversion long; fills book gaps (S.20)</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>SV_Hurst_L</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>SINGLE-VARIABLE</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Trend-persistence long; sizes book longs 2x + gap-fills (S.20)</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>8.960000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4767,7 +4943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4953,6 +5129,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>SV-gap</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>single-variable gap entry (S.20): fires only when zero Dots positions open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/foundational_documents/DOT_signal_dictionary.xlsx
+++ b/foundational_documents/DOT_signal_dictionary.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alphabetical Lookup" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime Cheat Sheet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name Key" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D2D" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +52,14 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +101,11 @@
         <fgColor rgb="00E8DAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -121,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,6 +165,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2688,6 +2706,32 @@
           <t>Micro_FailedBreak:hi@p90 · D2D- (LOCK=3)</t>
         </is>
       </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="18" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="n"/>
+      <c r="B68" s="17" t="n"/>
+      <c r="C68" s="17" t="n"/>
+      <c r="D68" s="17" t="n"/>
+      <c r="E68" s="17" t="n"/>
+      <c r="F68" s="17" t="n"/>
+      <c r="G68" s="17" t="n"/>
+      <c r="H68" s="17" t="n"/>
+      <c r="I68" s="17" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="n"/>
+      <c r="B69" s="17" t="n"/>
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="17" t="n"/>
+      <c r="F69" s="17" t="n"/>
+      <c r="G69" s="17" t="n"/>
+      <c r="H69" s="17" t="n"/>
+      <c r="I69" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4943,7 +4987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5141,7 +5185,431 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>D2D-conv</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>D2D-conviction 2x sizer (S.21): up-sizes a book trade both directions on a D2D throne-flip; only short conviction source</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>D2D-gap</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>D2D gap-filler (S.21): flat 2-lot standalone D2D throne entry when zero Dots open (bypasses conviction, no 4x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>D2D</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>D2D Break-of-Structure (9th market structure — the founding adaptive break-of-structure / directional-flip engine)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>D2D — THE FOUNDING SYSTEM (adaptive break-of-structure / directional-flip engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Anthony's original custom-OBVf-driven directional system, live in equiDOT.cs; ratified TM (native SuperTrend trail FORBIDDEN). The 9th market structure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>STANDALONE THRONE SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>32 (18L / 14S)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>both directions</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>96.9%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>one loss in ~5 months (a single -$153 SL, in March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16.89</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net P&amp;L $</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2,431</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1-lot base, true $1/pt (STANDALONE — separate from the $92,347 combined system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Worst Day $</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-153.0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>inside the FTMO -$2,500 daily gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Max Drawdown $</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-153.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Folds positive / min-fold PF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6/6 / 1.72</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>March holds the lone loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OOS (May-Jun)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>n12, 100% WR, PF 999, net $1,111</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>no OOS losers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Exit mix</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SL 1 (-153) / BE 25 (850) / LF 6 (1,734)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>the runner (LF) carries the net</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Per-fold PF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jan 999 / Feb 999 / Mar 1.72 / Apr 999 / May 999 / Jun 999</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>LONG / SHORT RULES (separate standalone configs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>WR% / PF</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Net $ / Worst Day / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D2D LONG-only</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>100.0% / 999</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$1,651 / +20 / NO losing day (max-DD 0.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D2D SHORT-only</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>92.9% / 6.10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$780 / -153 / the lone system loss is here (March)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>ROLES IN THE COMBINED SYSTEM (S.21 crown jewel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C1 D2D-Conviction</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2x sizer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>D2D_Signal==dir &amp; ADX&gt;=30 &amp; Micro_Hurst&gt;=p30 -&gt; up-size a book trade 2x (higher-mult-wins, never 4x); the ONLY short conviction source</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G1 D2D-Gap-Filler</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>flat-2-lot</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>throne entry fired when zero Dots open -&gt; flat 2.0 lots, bypasses conviction (no 4x); 14 trades (4L/10S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Crown-jewel contribution: Role 2 conviction +$1,015 + Role 1 gap +$1,900 -&gt; combined DOT+D2D system $92,347 (verified DIRECTLY, not summed). This tab records the STANDALONE object; $92,347 is the combined-system canonical.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/foundational_documents/DOT_signal_dictionary.xlsx
+++ b/foundational_documents/DOT_signal_dictionary.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,7 @@
     <font>
       <i val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="10">
     <fill>
@@ -133,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +172,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2707,7 +2709,6 @@
         </is>
       </c>
     </row>
-    <row r="66"/>
     <row r="67">
       <c r="A67" s="18" t="n"/>
     </row>
@@ -5232,7 +5233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5291,7 +5292,6 @@
           <t>32 (18L / 14S)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>both directions</t>
@@ -5309,7 +5309,6 @@
           <t>96.9%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>one loss in ~5 months (a single -$153 SL, in March)</t>
@@ -5327,8 +5326,6 @@
           <t>16.89</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5341,7 +5338,6 @@
           <t>2,431</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>1-lot base, true $1/pt (STANDALONE — separate from the $92,347 combined system)</t>
@@ -5359,7 +5355,6 @@
           <t>-153.0</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>inside the FTMO -$2,500 daily gate</t>
@@ -5377,8 +5372,6 @@
           <t>-153.0</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5391,7 +5384,6 @@
           <t>6/6 / 1.72</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>March holds the lone loss</t>
@@ -5409,7 +5401,6 @@
           <t>n12, 100% WR, PF 999, net $1,111</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>no OOS losers</t>
@@ -5427,7 +5418,6 @@
           <t>SL 1 (-153) / BE 25 (850) / LF 6 (1,734)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>the runner (LF) carries the net</t>
@@ -5445,8 +5435,6 @@
           <t>Jan 999 / Feb 999 / Mar 1.72 / Apr 999 / May 999 / Jun 999</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
@@ -5598,6 +5586,34 @@
       <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Crown-jewel contribution: Role 2 conviction +$1,015 + Role 1 gap +$1,900 -&gt; combined DOT+D2D system $92,347 (verified DIRECTLY, not summed). This tab records the STANDALONE object; $92,347 is the combined-system canonical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>!! 2026-07-27 EXPORT-CLOCK NOTE — EVERY FIGURE ON THIS SHEET WAS MEASURED WITH FRIDAY AFTERNOONS EXCLUDED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>DOT.cs L730-731 exported a clock 2-3h fast (the bar's SERVER time was fed into a parameter declared gmtTime), so portfolio_simulation_engine.py L148's Friday gate fired from true 13:00 EST instead of 16:45 and removed roughly the last three hours of every Friday cash session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Corrected-clock re-score of the same sealed-baseline window: 2,739 tr / WR 91.9% / PF 5.92 / net $91,506 (+41 tr, -$789 vs the $92,296 the recorded $92,347 reproduces at on the broken clock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>THE FIGURES ON THIS SHEET STAND AS THE HISTORICAL RECORD — they are NOT corrected-clock numbers. The LIVE EA clock was always correct. Law: S.22 non_negotiables_developer.txt. Detail: DOT_codebase_map.md section 5.</t>
         </is>
       </c>
     </row>
